--- a/data/curriculum_graduate.xlsx
+++ b/data/curriculum_graduate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/revelunt/Library/CloudStorage/Dropbox/0. 학부장 업무/학부홈페이지 개편/홈페이지 개편 시안/INDEX/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86622CBC-46DC-FB4C-91C0-D3374882CAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F473661-6CA4-DF4B-B33B-25C245EBCE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14080" yWindow="3640" windowWidth="29520" windowHeight="20200" activeTab="1" xr2:uid="{21A94480-1307-1043-865D-B691F327BBE6}"/>
+    <workbookView xWindow="14080" yWindow="3640" windowWidth="29520" windowHeight="20200" xr2:uid="{21A94480-1307-1043-865D-B691F327BBE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="129">
   <si>
     <t>종별</t>
   </si>
@@ -402,10 +402,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>연401</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>기초통계</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -418,36 +414,38 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>광고이론연구</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>온라인저널리즘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴미디어심리학</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>빌302</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴미디어와사회II</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>회귀분석</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>광고와사회</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2026-1</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강태우</t>
+  </si>
+  <si>
+    <t>COM6621</t>
+  </si>
+  <si>
+    <t>광고와미디어테크놀로지</t>
+  </si>
+  <si>
+    <t>COM6622</t>
+  </si>
+  <si>
+    <t>생성형AI와커뮤니케이션연구</t>
+  </si>
+  <si>
+    <t>내용분석</t>
+  </si>
+  <si>
+    <t>목</t>
+  </si>
+  <si>
+    <t>금</t>
+  </si>
+  <si>
+    <t>위기위험커뮤니케이션</t>
+  </si>
+  <si>
+    <t>2026-2</t>
   </si>
 </sst>
 </file>
@@ -1885,13 +1883,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91807FF8-03B3-1844-BD16-33C96DBD8A94}">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:14" ht="18">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1929,10 +1927,13 @@
         <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>118</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="14" t="s">
         <v>15</v>
       </c>
@@ -1962,8 +1963,9 @@
         <v>29</v>
       </c>
       <c r="M2" s="44"/>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" s="11"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="18" t="s">
         <v>15</v>
       </c>
@@ -1987,8 +1989,9 @@
       <c r="K3" s="7"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="18" t="s">
         <v>15</v>
       </c>
@@ -2018,8 +2021,9 @@
       <c r="K4" s="7"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="18" t="s">
         <v>15</v>
       </c>
@@ -2043,8 +2047,9 @@
         <v>21</v>
       </c>
       <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="18" t="s">
         <v>15</v>
       </c>
@@ -2068,8 +2073,11 @@
         <v>19</v>
       </c>
       <c r="M6" s="11"/>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="26" t="s">
         <v>17</v>
       </c>
@@ -2109,8 +2117,11 @@
       <c r="M7" s="17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="26" t="s">
         <v>17</v>
       </c>
@@ -2150,8 +2161,11 @@
       <c r="M8" s="36" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" s="35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="22" t="s">
         <v>15</v>
       </c>
@@ -2179,8 +2193,9 @@
       <c r="K9" s="17"/>
       <c r="L9" s="16"/>
       <c r="M9" s="43"/>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="22" t="s">
         <v>15</v>
       </c>
@@ -2208,8 +2223,11 @@
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="43"/>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="22" t="s">
         <v>15</v>
       </c>
@@ -2235,8 +2253,9 @@
       <c r="K11" s="17"/>
       <c r="L11" s="16"/>
       <c r="M11" s="43"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="16"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="22" t="s">
         <v>15</v>
       </c>
@@ -2264,8 +2283,9 @@
       <c r="M12" s="17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="22" t="s">
         <v>15</v>
       </c>
@@ -2289,8 +2309,9 @@
       <c r="K13" s="7"/>
       <c r="L13" s="11"/>
       <c r="M13" s="43"/>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="22" t="s">
         <v>15</v>
       </c>
@@ -2320,8 +2341,11 @@
         <v>13</v>
       </c>
       <c r="M14" s="43"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="22" t="s">
         <v>15</v>
       </c>
@@ -2353,8 +2377,9 @@
       <c r="M15" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" s="16"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="26" t="s">
         <v>17</v>
       </c>
@@ -2394,8 +2419,11 @@
       <c r="M16" s="17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="22" t="s">
         <v>15</v>
       </c>
@@ -2419,8 +2447,9 @@
       <c r="K17" s="17"/>
       <c r="L17" s="16"/>
       <c r="M17" s="43"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="16"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="22" t="s">
         <v>15</v>
       </c>
@@ -2446,8 +2475,9 @@
       <c r="K18" s="17"/>
       <c r="L18" s="16"/>
       <c r="M18" s="43"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="16"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="22" t="s">
         <v>15</v>
       </c>
@@ -2481,8 +2511,9 @@
       <c r="M19" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="16"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="22" t="s">
         <v>15</v>
       </c>
@@ -2510,8 +2541,11 @@
         <v>14</v>
       </c>
       <c r="M20" s="43"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="22" t="s">
         <v>15</v>
       </c>
@@ -2535,8 +2569,9 @@
       <c r="K21" s="17"/>
       <c r="L21" s="16"/>
       <c r="M21" s="43"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="16"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="22" t="s">
         <v>15</v>
       </c>
@@ -2562,8 +2597,9 @@
       <c r="K22" s="7"/>
       <c r="L22" s="11"/>
       <c r="M22" s="43"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="22" t="s">
         <v>15</v>
       </c>
@@ -2589,8 +2625,11 @@
         <v>30</v>
       </c>
       <c r="M23" s="43"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="22" t="s">
         <v>15</v>
       </c>
@@ -2618,8 +2657,9 @@
       <c r="K24" s="17"/>
       <c r="L24" s="16"/>
       <c r="M24" s="43"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="16"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="22" t="s">
         <v>15</v>
       </c>
@@ -2647,8 +2687,9 @@
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="43"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="16"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="22" t="s">
         <v>15</v>
       </c>
@@ -2674,8 +2715,9 @@
       <c r="M26" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="22" t="s">
         <v>15</v>
       </c>
@@ -2701,8 +2743,11 @@
       <c r="K27" s="17"/>
       <c r="L27" s="16"/>
       <c r="M27" s="43"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="22" t="s">
         <v>15</v>
       </c>
@@ -2728,8 +2773,9 @@
       <c r="M28" s="17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="16"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="22" t="s">
         <v>15</v>
       </c>
@@ -2753,8 +2799,9 @@
       <c r="K29" s="7"/>
       <c r="L29" s="11"/>
       <c r="M29" s="43"/>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="11"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="22" t="s">
         <v>15</v>
       </c>
@@ -2782,8 +2829,9 @@
       <c r="M30" s="17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="16"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="22" t="s">
         <v>15</v>
       </c>
@@ -2807,8 +2855,9 @@
       <c r="K31" s="17"/>
       <c r="L31" s="16"/>
       <c r="M31" s="43"/>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" s="16"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="22" t="s">
         <v>15</v>
       </c>
@@ -2834,8 +2883,9 @@
         <v>27</v>
       </c>
       <c r="M32" s="43"/>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" s="11"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="22" t="s">
         <v>15</v>
       </c>
@@ -2861,8 +2911,9 @@
       <c r="M33" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="16"/>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="22" t="s">
         <v>15</v>
       </c>
@@ -2886,8 +2937,11 @@
       </c>
       <c r="L34" s="16"/>
       <c r="M34" s="43"/>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="22" t="s">
         <v>15</v>
       </c>
@@ -2911,8 +2965,9 @@
       </c>
       <c r="L35" s="16"/>
       <c r="M35" s="43"/>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35" s="16"/>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="22" t="s">
         <v>15</v>
       </c>
@@ -2936,6 +2991,59 @@
       </c>
       <c r="L36" s="16"/>
       <c r="M36" s="43"/>
+      <c r="N36" s="16"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="24">
+        <v>3</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="24">
+        <v>3</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="17" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2971,13 +3079,13 @@
         <v>111</v>
       </c>
       <c r="I1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="L1" t="s">
         <v>113</v>
@@ -3003,13 +3111,13 @@
         <v>110</v>
       </c>
       <c r="I2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L2" t="s">
         <v>110</v>
@@ -3031,14 +3139,18 @@
       <c r="B4" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="42"/>
+      <c r="E4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" t="s">
         <v>116</v>
       </c>
-      <c r="K4" t="s">
-        <v>125</v>
-      </c>
       <c r="L4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="23">
@@ -3048,14 +3160,18 @@
       <c r="B5" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="42"/>
+      <c r="E5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" t="s">
         <v>116</v>
       </c>
-      <c r="K5" t="s">
-        <v>125</v>
-      </c>
       <c r="L5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="23">
@@ -3065,14 +3181,18 @@
       <c r="B6" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="42"/>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" t="s">
         <v>116</v>
       </c>
-      <c r="K6" t="s">
-        <v>125</v>
-      </c>
       <c r="L6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="23">
@@ -3083,10 +3203,7 @@
         <v>103</v>
       </c>
       <c r="C7" s="42"/>
-      <c r="F7" t="s">
-        <v>118</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="J7" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3097,20 +3214,22 @@
       <c r="B8" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I8" t="s">
-        <v>123</v>
-      </c>
-      <c r="K8" t="s">
-        <v>121</v>
-      </c>
-      <c r="L8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J8" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3121,22 +3240,25 @@
       <c r="B9" s="40" t="s">
         <v>105</v>
       </c>
+      <c r="C9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" t="s">
-        <v>123</v>
-      </c>
-      <c r="K9" t="s">
-        <v>121</v>
-      </c>
-      <c r="L9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3147,17 +3269,23 @@
       <c r="B10" s="40" t="s">
         <v>106</v>
       </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K10" t="s">
-        <v>121</v>
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="23">
@@ -3167,8 +3295,8 @@
       <c r="B11" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="E11" t="s">
-        <v>120</v>
+      <c r="D11" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/curriculum_graduate.xlsx
+++ b/data/curriculum_graduate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/revelunt/Library/CloudStorage/Dropbox/0. 학부장 업무/학부홈페이지 개편/홈페이지 개편 시안/INDEX/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyunjinsong/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F473661-6CA4-DF4B-B33B-25C245EBCE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A2378E-B927-E84C-B34D-8C73E1486DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14080" yWindow="3640" windowWidth="29520" windowHeight="20200" xr2:uid="{21A94480-1307-1043-865D-B691F327BBE6}"/>
+    <workbookView xWindow="14080" yWindow="3640" windowWidth="29520" windowHeight="20200" activeTab="1" xr2:uid="{21A94480-1307-1043-865D-B691F327BBE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="130">
   <si>
     <t>종별</t>
   </si>
@@ -446,6 +446,10 @@
   </si>
   <si>
     <t>2026-2</t>
+  </si>
+  <si>
+    <t>대별B102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -453,13 +457,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -473,7 +477,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -549,7 +553,7 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -881,7 +885,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -922,7 +926,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -938,7 +942,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -958,11 +962,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="4" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="4" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1012,7 +1016,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{967C6097-E765-AA47-AAE7-2C834FEA7F0E}"/>
     <cellStyle name="표준 2 2" xfId="2" xr:uid="{F60A35B3-DBAC-EA4E-A552-2D47C30D1C57}"/>
   </cellStyles>
@@ -1401,7 +1405,7 @@
         <charset val="129"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="0_ "/>
+      <numFmt numFmtId="176" formatCode="0_ "/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1567,7 +1571,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1884,12 +1888,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91807FF8-03B3-1844-BD16-33C96DBD8A94}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18">
+    <row r="1" spans="1:14">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3057,7 +3061,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB231238-78A9-E54C-808E-E7D7DF578189}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="C1" t="s">
@@ -3093,7 +3097,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="C2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
         <v>110</v>
@@ -3123,7 +3127,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="23">
+    <row r="3" spans="1:12" ht="24">
       <c r="A3" s="37">
         <v>1</v>
       </c>
@@ -3132,7 +3136,7 @@
       </c>
       <c r="C3" s="42"/>
     </row>
-    <row r="4" spans="1:12" ht="23">
+    <row r="4" spans="1:12" ht="24">
       <c r="A4" s="39">
         <v>2</v>
       </c>
@@ -3153,7 +3157,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="23">
+    <row r="5" spans="1:12" ht="24">
       <c r="A5" s="39">
         <v>3</v>
       </c>
@@ -3174,7 +3178,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="23">
+    <row r="6" spans="1:12" ht="24">
       <c r="A6" s="39">
         <v>4</v>
       </c>
@@ -3195,7 +3199,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="23">
+    <row r="7" spans="1:12" ht="24">
       <c r="A7" s="39">
         <v>5</v>
       </c>
@@ -3207,7 +3211,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="23">
+    <row r="8" spans="1:12" ht="24">
       <c r="A8" s="39">
         <v>6</v>
       </c>
@@ -3233,7 +3237,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="23">
+    <row r="9" spans="1:12" ht="24">
       <c r="A9" s="39">
         <v>7</v>
       </c>
@@ -3262,7 +3266,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="23">
+    <row r="10" spans="1:12" ht="24">
       <c r="A10" s="39">
         <v>8</v>
       </c>
@@ -3288,7 +3292,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="23">
+    <row r="11" spans="1:12" ht="24">
       <c r="A11" s="41">
         <v>9</v>
       </c>
